--- a/customers/amir mahdi.xlsx
+++ b/customers/amir mahdi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="43">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -142,6 +142,12 @@
   </si>
   <si>
     <t>جمع کل حساب احتساب اخرین فاکتور :</t>
+  </si>
+  <si>
+    <t>1405/04/19</t>
+  </si>
+  <si>
+    <t>دنگ کیک رضا</t>
   </si>
 </sst>
 </file>
@@ -629,7 +635,7 @@
       </c>
       <c r="H2" s="7">
         <f>C43</f>
-        <v>0</v>
+        <v>85000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1066,17 +1072,23 @@
     <row r="32" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="B32" s="6"/>
+        <v>85000</v>
+      </c>
+      <c r="B32" s="6">
+        <v>85000</v>
+      </c>
       <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="10"/>
+      <c r="D32" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="33" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -1086,7 +1098,7 @@
     <row r="34" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -1096,7 +1108,7 @@
     <row r="35" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -1106,7 +1118,7 @@
     <row r="36" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -1116,7 +1128,7 @@
     <row r="37" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -1126,7 +1138,7 @@
     <row r="38" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -1136,7 +1148,7 @@
     <row r="39" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -1146,7 +1158,7 @@
     <row r="40" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -1156,7 +1168,7 @@
     <row r="41" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -1166,7 +1178,7 @@
     <row r="42" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="7">
         <f>SUM(B22:B41)+B16</f>
-        <v>1508000</v>
+        <v>1593000</v>
       </c>
       <c r="C42" s="7">
         <f>SUM(C22:C41)+C16</f>
@@ -1178,7 +1190,7 @@
       <c r="B43" s="7"/>
       <c r="C43" s="9">
         <f xml:space="preserve"> A41</f>
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>40</v>

--- a/customers/amir mahdi.xlsx
+++ b/customers/amir mahdi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="44">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -148,6 +148,9 @@
   </si>
   <si>
     <t>دنگ کیک رضا</t>
+  </si>
+  <si>
+    <t>1405/06/05</t>
   </si>
 </sst>
 </file>
@@ -635,7 +638,7 @@
       </c>
       <c r="H2" s="7">
         <f>C43</f>
-        <v>85000</v>
+        <v>220000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1088,17 +1091,23 @@
     <row r="33" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6">
         <f t="shared" si="1"/>
-        <v>85000</v>
-      </c>
-      <c r="B33" s="6"/>
+        <v>220000</v>
+      </c>
+      <c r="B33" s="6">
+        <v>135000</v>
+      </c>
       <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="10"/>
+      <c r="D33" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="34" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6">
         <f t="shared" si="1"/>
-        <v>85000</v>
+        <v>220000</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -1108,7 +1117,7 @@
     <row r="35" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
         <f t="shared" si="1"/>
-        <v>85000</v>
+        <v>220000</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -1118,7 +1127,7 @@
     <row r="36" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6">
         <f t="shared" si="1"/>
-        <v>85000</v>
+        <v>220000</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -1128,7 +1137,7 @@
     <row r="37" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <f t="shared" si="1"/>
-        <v>85000</v>
+        <v>220000</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -1138,7 +1147,7 @@
     <row r="38" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <f t="shared" si="1"/>
-        <v>85000</v>
+        <v>220000</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -1148,7 +1157,7 @@
     <row r="39" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <f t="shared" si="1"/>
-        <v>85000</v>
+        <v>220000</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -1158,7 +1167,7 @@
     <row r="40" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <f t="shared" si="1"/>
-        <v>85000</v>
+        <v>220000</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -1168,7 +1177,7 @@
     <row r="41" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <f t="shared" si="1"/>
-        <v>85000</v>
+        <v>220000</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -1178,7 +1187,7 @@
     <row r="42" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="7">
         <f>SUM(B22:B41)+B16</f>
-        <v>1593000</v>
+        <v>1728000</v>
       </c>
       <c r="C42" s="7">
         <f>SUM(C22:C41)+C16</f>
@@ -1190,7 +1199,7 @@
       <c r="B43" s="7"/>
       <c r="C43" s="9">
         <f xml:space="preserve"> A41</f>
-        <v>85000</v>
+        <v>220000</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>40</v>

--- a/customers/amir mahdi.xlsx
+++ b/customers/amir mahdi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="45">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -151,6 +151,9 @@
   </si>
   <si>
     <t>1405/06/05</t>
+  </si>
+  <si>
+    <t>1405/06/07</t>
   </si>
 </sst>
 </file>
@@ -638,7 +641,7 @@
       </c>
       <c r="H2" s="7">
         <f>C43</f>
-        <v>220000</v>
+        <v>355000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1107,17 +1110,23 @@
     <row r="34" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6">
         <f t="shared" si="1"/>
-        <v>220000</v>
-      </c>
-      <c r="B34" s="6"/>
+        <v>355000</v>
+      </c>
+      <c r="B34" s="6">
+        <v>135000</v>
+      </c>
       <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="10"/>
+      <c r="D34" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="35" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
         <f t="shared" si="1"/>
-        <v>220000</v>
+        <v>355000</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -1127,7 +1136,7 @@
     <row r="36" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6">
         <f t="shared" si="1"/>
-        <v>220000</v>
+        <v>355000</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -1137,7 +1146,7 @@
     <row r="37" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <f t="shared" si="1"/>
-        <v>220000</v>
+        <v>355000</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -1147,7 +1156,7 @@
     <row r="38" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <f t="shared" si="1"/>
-        <v>220000</v>
+        <v>355000</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -1157,7 +1166,7 @@
     <row r="39" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <f t="shared" si="1"/>
-        <v>220000</v>
+        <v>355000</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -1167,7 +1176,7 @@
     <row r="40" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <f t="shared" si="1"/>
-        <v>220000</v>
+        <v>355000</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -1177,7 +1186,7 @@
     <row r="41" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <f t="shared" si="1"/>
-        <v>220000</v>
+        <v>355000</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -1187,7 +1196,7 @@
     <row r="42" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="7">
         <f>SUM(B22:B41)+B16</f>
-        <v>1728000</v>
+        <v>1863000</v>
       </c>
       <c r="C42" s="7">
         <f>SUM(C22:C41)+C16</f>
@@ -1199,7 +1208,7 @@
       <c r="B43" s="7"/>
       <c r="C43" s="9">
         <f xml:space="preserve"> A41</f>
-        <v>220000</v>
+        <v>355000</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>40</v>

--- a/customers/amir mahdi.xlsx
+++ b/customers/amir mahdi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="46">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -154,6 +154,9 @@
   </si>
   <si>
     <t>1405/06/07</t>
+  </si>
+  <si>
+    <t>1405/06/11</t>
   </si>
 </sst>
 </file>
@@ -641,7 +644,7 @@
       </c>
       <c r="H2" s="7">
         <f>C43</f>
-        <v>355000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1126,17 +1129,23 @@
     <row r="35" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
         <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6">
         <v>355000</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="10"/>
+      <c r="D35" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="36" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6">
         <f t="shared" si="1"/>
-        <v>355000</v>
+        <v>0</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -1146,7 +1155,7 @@
     <row r="37" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <f t="shared" si="1"/>
-        <v>355000</v>
+        <v>0</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -1156,7 +1165,7 @@
     <row r="38" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <f t="shared" si="1"/>
-        <v>355000</v>
+        <v>0</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -1166,7 +1175,7 @@
     <row r="39" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <f t="shared" si="1"/>
-        <v>355000</v>
+        <v>0</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -1176,7 +1185,7 @@
     <row r="40" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <f t="shared" si="1"/>
-        <v>355000</v>
+        <v>0</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -1186,7 +1195,7 @@
     <row r="41" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <f t="shared" si="1"/>
-        <v>355000</v>
+        <v>0</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -1200,7 +1209,7 @@
       </c>
       <c r="C42" s="7">
         <f>SUM(C22:C41)+C16</f>
-        <v>1508000</v>
+        <v>1863000</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -1208,7 +1217,7 @@
       <c r="B43" s="7"/>
       <c r="C43" s="9">
         <f xml:space="preserve"> A41</f>
-        <v>355000</v>
+        <v>0</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>40</v>

--- a/customers/amir mahdi.xlsx
+++ b/customers/amir mahdi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="47">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -157,6 +157,9 @@
   </si>
   <si>
     <t>1405/06/11</t>
+  </si>
+  <si>
+    <t>1405/06/18</t>
   </si>
 </sst>
 </file>
@@ -644,7 +647,7 @@
       </c>
       <c r="H2" s="7">
         <f>C43</f>
-        <v>0</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1145,17 +1148,23 @@
     <row r="36" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="B36" s="6"/>
+        <v>150000</v>
+      </c>
+      <c r="B36" s="6">
+        <v>150000</v>
+      </c>
       <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="10"/>
+      <c r="D36" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="37" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -1165,7 +1174,7 @@
     <row r="38" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -1175,7 +1184,7 @@
     <row r="39" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -1185,7 +1194,7 @@
     <row r="40" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -1195,7 +1204,7 @@
     <row r="41" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -1205,7 +1214,7 @@
     <row r="42" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="7">
         <f>SUM(B22:B41)+B16</f>
-        <v>1863000</v>
+        <v>2013000</v>
       </c>
       <c r="C42" s="7">
         <f>SUM(C22:C41)+C16</f>
@@ -1217,7 +1226,7 @@
       <c r="B43" s="7"/>
       <c r="C43" s="9">
         <f xml:space="preserve"> A41</f>
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>40</v>

--- a/customers/amir mahdi.xlsx
+++ b/customers/amir mahdi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -160,6 +160,12 @@
   </si>
   <si>
     <t>1405/06/18</t>
+  </si>
+  <si>
+    <t>1405/06/21</t>
+  </si>
+  <si>
+    <t>دنگ کشمش</t>
   </si>
 </sst>
 </file>
@@ -647,7 +653,7 @@
       </c>
       <c r="H2" s="7">
         <f>C43</f>
-        <v>150000</v>
+        <v>580000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1164,17 +1170,23 @@
     <row r="37" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <f t="shared" si="1"/>
-        <v>150000</v>
-      </c>
-      <c r="B37" s="6"/>
+        <v>580000</v>
+      </c>
+      <c r="B37" s="6">
+        <v>430000</v>
+      </c>
       <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="10"/>
+      <c r="D37" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="38" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <f t="shared" si="1"/>
-        <v>150000</v>
+        <v>580000</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -1184,7 +1196,7 @@
     <row r="39" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <f t="shared" si="1"/>
-        <v>150000</v>
+        <v>580000</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -1194,7 +1206,7 @@
     <row r="40" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <f t="shared" si="1"/>
-        <v>150000</v>
+        <v>580000</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -1204,7 +1216,7 @@
     <row r="41" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <f t="shared" si="1"/>
-        <v>150000</v>
+        <v>580000</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -1214,7 +1226,7 @@
     <row r="42" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="7">
         <f>SUM(B22:B41)+B16</f>
-        <v>2013000</v>
+        <v>2443000</v>
       </c>
       <c r="C42" s="7">
         <f>SUM(C22:C41)+C16</f>
@@ -1226,7 +1238,7 @@
       <c r="B43" s="7"/>
       <c r="C43" s="9">
         <f xml:space="preserve"> A41</f>
-        <v>150000</v>
+        <v>580000</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>40</v>
